--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.114.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.114.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.114.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.114.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -605,24 +605,28 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]107</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]107</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L29: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L3: isolated marker/symbol line :: 1</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]107</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -657,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,12 +672,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: viz.â€”.</t>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L3: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -728,7 +732,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: viz.â€”.</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -740,7 +744,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -779,19 +783,19 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L45: symbol-only separator/garbage line :: 1837.</t>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -833,10 +837,14 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 107</t>
-        </is>
-      </c>
-      <c r="O6" s="1" t="inlineStr"/>
+          <t>L45: symbol-only separator/garbage line :: 1837.</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
@@ -876,7 +884,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L100: symbol-only separator/garbage line :: 1850.</t>
+          <t>L48: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -919,7 +927,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: +</t>
+          <t>L100: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -962,7 +970,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L106: symbol-only separator/garbage line :: 1850.</t>
+          <t>L105: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -1005,7 +1013,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L141: symbol-only separator/garbage line :: (7).</t>
+          <t>L106: symbol-only separator/garbage line :: 1850.</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1033,7 +1041,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1046,7 +1054,11 @@
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>L141: symbol-only separator/garbage line :: (7).</t>
+        </is>
+      </c>
       <c r="O11" s="1" t="inlineStr"/>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
@@ -1067,12 +1079,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
